--- a/docs/templates/plantilla-proyectos.xlsx
+++ b/docs/templates/plantilla-proyectos.xlsx
@@ -392,10 +392,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="13" width="26" style="1" customWidth="1"/>
+    <col min="1" max="26" width="26" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="str">
         <v>Nombre del proyecto</v>
       </c>
@@ -403,37 +403,76 @@
         <v>Código CRM del cliente</v>
       </c>
       <c r="C1" s="3" t="str">
-        <v>País</v>
+        <v>Código de cliente</v>
       </c>
       <c r="D1" s="3" t="str">
+        <v>País</v>
+      </c>
+      <c r="E1" s="3" t="str">
         <v>Ciudad</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="F1" s="3" t="str">
         <v>Dirección</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="G1" s="3" t="str">
         <v>Descripción</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="H1" s="3" t="str">
         <v>Fecha estimada de inicio</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="I1" s="3" t="str">
         <v>Fecha estimada de fin</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="J1" s="3" t="str">
         <v>Fecha estimada de decisión</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="K1" s="3" t="str">
         <v>Responsable</v>
       </c>
-      <c r="K1" s="3" t="str">
-        <v>Tipo de proyecto</v>
-      </c>
       <c r="L1" s="3" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="M1" s="3" t="str">
         <v>Sector</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="N1" s="3" t="str">
         <v>Código de proyecto</v>
+      </c>
+      <c r="O1" s="3" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="P1" s="3" t="str">
+        <v>Cantidad estimada</v>
+      </c>
+      <c r="Q1" s="3" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="R1" s="3" t="str">
+        <v>Avance de fase</v>
+      </c>
+      <c r="S1" s="3" t="str">
+        <v>Comentario de fase</v>
+      </c>
+      <c r="T1" s="3" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="U1" s="3" t="str">
+        <v>Fecha de oportunidad</v>
+      </c>
+      <c r="V1" s="3" t="str">
+        <v>Resultado</v>
+      </c>
+      <c r="W1" s="3" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="X1" s="3" t="str">
+        <v>Porcentaje adjudicado</v>
+      </c>
+      <c r="Y1" s="3" t="str">
+        <v>Fecha de decisión</v>
+      </c>
+      <c r="Z1" s="3" t="str">
+        <v>Comentario del resultado</v>
       </c>
     </row>
   </sheetData>
@@ -502,10 +541,10 @@
         <v>Código CRM del cliente</v>
       </c>
       <c r="C3" s="1" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
       <c r="D3" s="1" t="str">
-        <v>Código CRM que el sistema asignó al cliente al crearlo (único en todo el sistema; se ve en la ficha del cliente). El cliente debe existir, estar activo y no estar eliminado.</v>
+        <v>Código CRM que el sistema asignó al cliente al crearlo (único en todo el sistema; se ve en la ficha del cliente). Indique este código o el código de cliente, no los dos. El cliente debe existir, estar activo y no estar eliminado.</v>
       </c>
       <c r="E3" s="1" t="str">
         <v>30</v>
@@ -519,17 +558,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B4" s="1" t="str">
-        <v>País</v>
+        <v>Código de cliente</v>
       </c>
       <c r="C4" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D4" s="1" t="str">
-        <v>Código ISO de dos letras de un país activo (ver hoja Valores válidos). Vacío: el país del cliente.</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>Código del cliente en el sistema de origen (el de la carga de clientes). Alternativa al código CRM. Si varios países tienen un cliente con ese código, indique el País.</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <v>40</v>
+      </c>
       <c r="F4" s="1" t="str">
-        <v>GT</v>
+        <v>90152</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -537,19 +578,17 @@
         <v>Proyectos</v>
       </c>
       <c r="B5" s="1" t="str">
-        <v>Ciudad</v>
+        <v>País</v>
       </c>
       <c r="C5" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Ciudad o ubicación, texto libre.</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <v>120</v>
-      </c>
+        <v>Código ISO de dos letras de un país activo (ver hoja Valores válidos). Vacío: el país del cliente.</v>
+      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1" t="str">
-        <v>Ciudad de Guatemala</v>
+        <v>GT</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,19 +596,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B6" s="1" t="str">
-        <v>Dirección</v>
+        <v>Ciudad</v>
       </c>
       <c r="C6" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D6" s="1" t="str">
-        <v>Dirección de la obra.</v>
+        <v>Ciudad o ubicación, texto libre.</v>
       </c>
       <c r="E6" s="1" t="str">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F6" s="1" t="str">
-        <v>Avenida 1, zona 1</v>
+        <v>Ciudad de Guatemala</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -577,19 +616,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B7" s="1" t="str">
-        <v>Descripción</v>
+        <v>Dirección</v>
       </c>
       <c r="C7" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D7" s="1" t="str">
-        <v>Descripción del proyecto.</v>
+        <v>Dirección de la obra.</v>
       </c>
       <c r="E7" s="1" t="str">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="F7" s="1" t="str">
-        <v>Proyecto ficticio de ejemplo</v>
+        <v>Avenida 1, zona 1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -597,19 +636,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B8" s="1" t="str">
-        <v>Fecha estimada de inicio</v>
+        <v>Descripción</v>
       </c>
       <c r="C8" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D8" s="1" t="str">
-        <v>Fecha AAAA-MM-DD. Escríbala como texto, no como fecha de Excel.</v>
+        <v>Descripción del proyecto.</v>
       </c>
       <c r="E8" s="1" t="str">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="1" t="str">
-        <v>2027-01-15</v>
+        <v>Proyecto ficticio de ejemplo</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -617,19 +656,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B9" s="1" t="str">
-        <v>Fecha estimada de fin</v>
+        <v>Fecha estimada de inicio</v>
       </c>
       <c r="C9" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D9" s="1" t="str">
-        <v>Fecha AAAA-MM-DD, igual o posterior a la de inicio.</v>
+        <v>Fecha AAAA-MM-DD. Escríbala como texto, no como fecha de Excel.</v>
       </c>
       <c r="E9" s="1" t="str">
         <v>10</v>
       </c>
       <c r="F9" s="1" t="str">
-        <v>2027-12-15</v>
+        <v>2027-01-15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -637,19 +676,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B10" s="1" t="str">
-        <v>Fecha estimada de decisión</v>
+        <v>Fecha estimada de fin</v>
       </c>
       <c r="C10" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D10" s="1" t="str">
-        <v>Fecha AAAA-MM-DD, sin restricción respecto a inicio y fin.</v>
+        <v>Fecha AAAA-MM-DD, igual o posterior a la de inicio.</v>
       </c>
       <c r="E10" s="1" t="str">
         <v>10</v>
       </c>
       <c r="F10" s="1" t="str">
-        <v>2026-12-01</v>
+        <v>2027-12-15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -657,19 +696,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B11" s="1" t="str">
-        <v>Responsable</v>
+        <v>Fecha estimada de decisión</v>
       </c>
       <c r="C11" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D11" s="1" t="str">
-        <v>Correo o código de colaborador de un usuario activo. Vacío: quien ejecuta la carga (--actor).</v>
+        <v>Fecha AAAA-MM-DD, sin restricción respecto a inicio y fin.</v>
       </c>
       <c r="E11" s="1" t="str">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="str">
-        <v>responsable@example.invalid</v>
+        <v>2026-12-01</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -677,17 +716,19 @@
         <v>Proyectos</v>
       </c>
       <c r="B12" s="1" t="str">
-        <v>Tipo de proyecto</v>
+        <v>Responsable</v>
       </c>
       <c r="C12" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D12" s="1" t="str">
-        <v>Código de un tipo de proyecto activo (ver hoja Valores válidos).</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>Correo o código de colaborador de un usuario activo. Vacío: quien ejecuta la carga (--actor).</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <v>320</v>
+      </c>
       <c r="F12" s="1" t="str">
-        <v>EDIFICIO</v>
+        <v>responsable@example.invalid</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -695,17 +736,17 @@
         <v>Proyectos</v>
       </c>
       <c r="B13" s="1" t="str">
-        <v>Sector</v>
+        <v>Tipo de proyecto</v>
       </c>
       <c r="C13" s="1" t="str">
         <v>No</v>
       </c>
       <c r="D13" s="1" t="str">
-        <v>Código de un sector de proyecto activo (ver hoja Valores válidos).</v>
+        <v>Código de un tipo de proyecto activo (ver hoja Valores válidos).</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="str">
-        <v>COMERCIAL</v>
+        <v>EDIFICIO</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -713,34 +754,278 @@
         <v>Proyectos</v>
       </c>
       <c r="B14" s="1" t="str">
+        <v>Sector</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <v>Código de un sector de proyecto activo (ver hoja Valores válidos).</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="str">
+        <v>COMERCIAL</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B15" s="1" t="str">
         <v>Código de proyecto</v>
       </c>
-      <c r="C14" s="1" t="str">
-        <v>No</v>
-      </c>
-      <c r="D14" s="1" t="str">
+      <c r="C15" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D15" s="1" t="str">
         <v>Opcional; si se deja vacío el sistema asigna el folio PRY-AAAA-nnnnn. Se guarda en mayúsculas y es único.</v>
       </c>
-      <c r="E14" s="1" t="str">
+      <c r="E15" s="1" t="str">
         <v>30</v>
       </c>
-      <c r="F14" s="1" t="str">
+      <c r="F15" s="1" t="str">
         <v>PRY-EJEMPLO-001</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <v>Código de una unidad de medida activa en la que se mide el proyecto (ver hoja Valores válidos). Obligatoria si hay cantidad estimada.</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <v>M2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <v>Cantidad estimada</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <v>Número mayor o igual a 0, con punto decimal y hasta 4 decimales, en la unidad de medida.</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="str">
+        <v>1250.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <v>Código de una fase del cliente activa (ver hoja Valores válidos). Vacío: la fase inicial por defecto.</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="str">
+        <v>CONSTRUCCION</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <v>Avance de fase</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <v>Porcentaje de avance de 0 a 100, hasta 2 decimales. Exige la fase del cliente.</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <v>Comentario de fase</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <v>Comentario del cambio de fase. Exige la fase del cliente.</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <v>Fase en el CRM anterior: Execution</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <v>Código de una etapa de oportunidad activa (ver hoja Valores válidos). Con valor se crea una oportunidad del proyecto, asignada a su responsable; vacío: sin oportunidad.</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="str">
+        <v>GANADO</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <v>Fecha de oportunidad</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <v>Fecha AAAA-MM-DD en que se identificó la oportunidad (los reportes la usan para ubicarla en su período). Vacío: hoy. Exige la etapa.</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <v>10</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <v>2024-03-10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <v>Resultado</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D23" s="1" t="str">
+        <v>WON (ganado), LOST (perdido) o PARTIAL (parcial). Obligatorio si la etapa es cerrada; no se admite con una etapa abierta.</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="str">
+        <v>WON</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B24" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D24" s="1" t="str">
+        <v>Código de un motivo de resultado activo que aplique al resultado (ver hoja Valores válidos). Obligatorio con LOST.</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="str">
+        <v>PRECIO</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B25" s="1" t="str">
+        <v>Porcentaje adjudicado</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <v>Porcentaje de 0 a 100, hasta 2 decimales. Obligatorio con PARTIAL.</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B26" s="1" t="str">
+        <v>Fecha de decisión</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <v>Fecha AAAA-MM-DD del resultado (los reportes de ganadas y perdidas la usan). Obligatoria con resultado.</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <v>10</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <v>2024-09-30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
+        <v>Proyectos</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <v>Comentario del resultado</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <v>Comentario del resultado. Exige el resultado.</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <v>2000</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <v>Motivo en el CRM anterior: Product price</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="str">
         <v>Versión de plantilla</v>
       </c>
-      <c r="B16" s="1" t="str">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="str">
+      <c r="B29" s="1" t="str">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="str">
         <v>Escriba los datos en las hojas de datos; todas las columnas deben estar presentes.</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -836,112 +1121,937 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
-        <v>Tipo de proyecto</v>
+        <v>País</v>
       </c>
       <c r="B8" s="1" t="str">
-        <v>VIVIENDA</v>
+        <v>US</v>
       </c>
       <c r="C8" s="1" t="str">
-        <v>Vivienda</v>
+        <v>Estados Unidos</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
-        <v>Tipo de proyecto</v>
+        <v>País</v>
       </c>
       <c r="B9" s="1" t="str">
-        <v>EDIFICIO</v>
+        <v>PR</v>
       </c>
       <c r="C9" s="1" t="str">
-        <v>Edificio</v>
+        <v>Puerto Rico</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
-        <v>Tipo de proyecto</v>
+        <v>País</v>
       </c>
       <c r="B10" s="1" t="str">
-        <v>INFRAESTRUCTURA</v>
+        <v>PA</v>
       </c>
       <c r="C10" s="1" t="str">
-        <v>Infraestructura</v>
+        <v>Panamá</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
-        <v>Tipo de proyecto</v>
+        <v>País</v>
       </c>
       <c r="B11" s="1" t="str">
-        <v>INDUSTRIAL</v>
+        <v>MX</v>
       </c>
       <c r="C11" s="1" t="str">
-        <v>Industrial</v>
+        <v>México</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
-        <v>Tipo de proyecto</v>
+        <v>País</v>
       </c>
       <c r="B12" s="1" t="str">
-        <v>COMERCIAL</v>
+        <v>CO</v>
       </c>
       <c r="C12" s="1" t="str">
-        <v>Comercial</v>
+        <v>Colombia</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
-        <v>Sector</v>
+        <v>País</v>
       </c>
       <c r="B13" s="1" t="str">
-        <v>RESIDENCIAL</v>
+        <v>PE</v>
       </c>
       <c r="C13" s="1" t="str">
-        <v>Residencial</v>
+        <v>Perú</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
-        <v>Sector</v>
+        <v>País</v>
       </c>
       <c r="B14" s="1" t="str">
-        <v>COMERCIAL</v>
+        <v>CL</v>
       </c>
       <c r="C14" s="1" t="str">
-        <v>Comercial</v>
+        <v>Chile</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
-        <v>Sector</v>
+        <v>País</v>
       </c>
       <c r="B15" s="1" t="str">
-        <v>INDUSTRIAL</v>
+        <v>BR</v>
       </c>
       <c r="C15" s="1" t="str">
-        <v>Industrial</v>
+        <v>Brasil</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
-        <v>Sector</v>
+        <v>País</v>
       </c>
       <c r="B16" s="1" t="str">
-        <v>PUBLICO</v>
+        <v>UY</v>
       </c>
       <c r="C16" s="1" t="str">
-        <v>Público</v>
+        <v>Uruguay</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <v>DO</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <v>República Dominicana</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <v>HT</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <v>Haití</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <v>JM</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <v>Jamaica</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <v>TT</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <v>Trinidad y Tobago</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <v>BB</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <v>Barbados</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <v>GY</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <v>Guyana</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <v>SR</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <v>Surinam</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B24" s="1" t="str">
+        <v>BE</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <v>Bélgica</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B25" s="1" t="str">
+        <v>DK</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <v>Dinamarca</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B26" s="1" t="str">
+        <v>IT</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <v>Italia</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <v>SK</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <v>Eslovaquia</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <v>CN</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <v>China</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="str">
+        <v>País</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <v>Indonesia</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <v>VIVIENDA</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <v>Vivienda</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B31" s="1" t="str">
+        <v>EDIFICIO</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <v>Edificio</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <v>INFRAESTRUCTURA</v>
+      </c>
+      <c r="C32" s="1" t="str">
+        <v>Infraestructura</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <v>INDUSTRIAL</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <v>Industrial</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B34" s="1" t="str">
+        <v>COMERCIAL</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <v>Comercial</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B35" s="1" t="str">
+        <v>LIVING_PLACES</v>
+      </c>
+      <c r="C35" s="1" t="str">
+        <v>Living Places / Houses</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B36" s="1" t="str">
+        <v>INDUSTRIAL_FLOORS</v>
+      </c>
+      <c r="C36" s="1" t="str">
+        <v>Industrial Floors</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B37" s="1" t="str">
+        <v>CONCRETE_INFRASTRUCTURE</v>
+      </c>
+      <c r="C37" s="1" t="str">
+        <v>Concrete Infrastructure</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B38" s="1" t="str">
+        <v>CONCRETE_BUILDINGS</v>
+      </c>
+      <c r="C38" s="1" t="str">
+        <v>Concrete Buildings</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B39" s="1" t="str">
+        <v>PRO_ENCLOSURE</v>
+      </c>
+      <c r="C39" s="1" t="str">
+        <v>Pro Enclosure</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B40" s="1" t="str">
+        <v>GABION_STABILISATION</v>
+      </c>
+      <c r="C40" s="1" t="str">
+        <v>Gabion Stabilisation</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B41" s="1" t="str">
+        <v>LINK_ENCLOSURE</v>
+      </c>
+      <c r="C41" s="1" t="str">
+        <v>Link Enclosure</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B42" s="1" t="str">
+        <v>PRECAST_BRIDGES</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <v>Precast Bridges</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B43" s="1" t="str">
+        <v>COMMERCE</v>
+      </c>
+      <c r="C43" s="1" t="str">
+        <v>Commerce</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B44" s="1" t="str">
+        <v>METAL_BUILDINGS</v>
+      </c>
+      <c r="C44" s="1" t="str">
+        <v>Metal Buildings</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B45" s="1" t="str">
+        <v>METAL_INFRASTRUCTURE</v>
+      </c>
+      <c r="C45" s="1" t="str">
+        <v>Metal Infrastructure</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B46" s="1" t="str">
+        <v>TUNNELS</v>
+      </c>
+      <c r="C46" s="1" t="str">
+        <v>Tunnels</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B47" s="1" t="str">
+        <v>SLOPE_STABILIZATION</v>
+      </c>
+      <c r="C47" s="1" t="str">
+        <v>Slope Stabilization</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B48" s="1" t="str">
+        <v>SANITARY</v>
+      </c>
+      <c r="C48" s="1" t="str">
+        <v>Sanitary</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B49" s="1" t="str">
+        <v>BEAM_ENCLOSURE</v>
+      </c>
+      <c r="C49" s="1" t="str">
+        <v>Beam Enclosure</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="str">
+        <v>Tipo de proyecto</v>
+      </c>
+      <c r="B50" s="1" t="str">
+        <v>MINING</v>
+      </c>
+      <c r="C50" s="1" t="str">
+        <v>Mining</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="str">
         <v>Sector</v>
       </c>
-      <c r="B17" s="1" t="str">
+      <c r="B51" s="1" t="str">
+        <v>RESIDENCIAL</v>
+      </c>
+      <c r="C51" s="1" t="str">
+        <v>Residencial</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="str">
+        <v>Sector</v>
+      </c>
+      <c r="B52" s="1" t="str">
+        <v>COMERCIAL</v>
+      </c>
+      <c r="C52" s="1" t="str">
+        <v>Comercial</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="str">
+        <v>Sector</v>
+      </c>
+      <c r="B53" s="1" t="str">
+        <v>INDUSTRIAL</v>
+      </c>
+      <c r="C53" s="1" t="str">
+        <v>Industrial</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="str">
+        <v>Sector</v>
+      </c>
+      <c r="B54" s="1" t="str">
+        <v>PUBLICO</v>
+      </c>
+      <c r="C54" s="1" t="str">
+        <v>Público</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="str">
+        <v>Sector</v>
+      </c>
+      <c r="B55" s="1" t="str">
         <v>MIXTO</v>
       </c>
-      <c r="C17" s="1" t="str">
+      <c r="C55" s="1" t="str">
         <v>Mixto</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B56" s="1" t="str">
+        <v>TON</v>
+      </c>
+      <c r="C56" s="1" t="str">
+        <v>Tonelada</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B57" s="1" t="str">
+        <v>KG</v>
+      </c>
+      <c r="C57" s="1" t="str">
+        <v>Kilogramo</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B58" s="1" t="str">
+        <v>LB</v>
+      </c>
+      <c r="C58" s="1" t="str">
+        <v>Libra</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B59" s="1" t="str">
+        <v>QQ</v>
+      </c>
+      <c r="C59" s="1" t="str">
+        <v>Quintal</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B60" s="1" t="str">
+        <v>M</v>
+      </c>
+      <c r="C60" s="1" t="str">
+        <v>Metro</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B61" s="1" t="str">
+        <v>M2</v>
+      </c>
+      <c r="C61" s="1" t="str">
+        <v>Metro cuadrado</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B62" s="1" t="str">
+        <v>M3</v>
+      </c>
+      <c r="C62" s="1" t="str">
+        <v>Metro cúbico</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B63" s="1" t="str">
+        <v>UND</v>
+      </c>
+      <c r="C63" s="1" t="str">
+        <v>Unidad</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B64" s="1" t="str">
+        <v>VAR</v>
+      </c>
+      <c r="C64" s="1" t="str">
+        <v>Varilla</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B65" s="1" t="str">
+        <v>KM</v>
+      </c>
+      <c r="C65" s="1" t="str">
+        <v>Kilómetro</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B66" s="1" t="str">
+        <v>PZA</v>
+      </c>
+      <c r="C66" s="1" t="str">
+        <v>Pieza</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B67" s="1" t="str">
+        <v>ROL</v>
+      </c>
+      <c r="C67" s="1" t="str">
+        <v>Rollo</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B68" s="1" t="str">
+        <v>CJS</v>
+      </c>
+      <c r="C68" s="1" t="str">
+        <v>Caja</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B69" s="1" t="str">
+        <v>PAQ</v>
+      </c>
+      <c r="C69" s="1" t="str">
+        <v>Paquete</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B70" s="1" t="str">
+        <v>SET</v>
+      </c>
+      <c r="C70" s="1" t="str">
+        <v>Juego</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="str">
+        <v>Unidad de medida</v>
+      </c>
+      <c r="B71" s="1" t="str">
+        <v>SAC</v>
+      </c>
+      <c r="C71" s="1" t="str">
+        <v>Saco</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="B72" s="1" t="str">
+        <v>DISENO</v>
+      </c>
+      <c r="C72" s="1" t="str">
+        <v>Diseño</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="B73" s="1" t="str">
+        <v>COTIZACION</v>
+      </c>
+      <c r="C73" s="1" t="str">
+        <v>Cotización</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="B74" s="1" t="str">
+        <v>CONSTRUCCION</v>
+      </c>
+      <c r="C74" s="1" t="str">
+        <v>Construcción</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="B75" s="1" t="str">
+        <v>FINALIZADO</v>
+      </c>
+      <c r="C75" s="1" t="str">
+        <v>Finalizado</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="B76" s="1" t="str">
+        <v>INICIAL</v>
+      </c>
+      <c r="C76" s="1" t="str">
+        <v>Inicial</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="str">
+        <v>Fase del cliente</v>
+      </c>
+      <c r="B77" s="1" t="str">
+        <v>PARALIZADO</v>
+      </c>
+      <c r="C77" s="1" t="str">
+        <v>Paralizado / en espera</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="B78" s="1" t="str">
+        <v>CONTACTADO</v>
+      </c>
+      <c r="C78" s="1" t="str">
+        <v>Contactado</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="B79" s="1" t="str">
+        <v>COTIZANDO</v>
+      </c>
+      <c r="C79" s="1" t="str">
+        <v>Cotizando</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="B80" s="1" t="str">
+        <v>GANADO</v>
+      </c>
+      <c r="C80" s="1" t="str">
+        <v>Ganado</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="B81" s="1" t="str">
+        <v>PERDIDO</v>
+      </c>
+      <c r="C81" s="1" t="str">
+        <v>Perdido</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="str">
+        <v>Etapa de oportunidad</v>
+      </c>
+      <c r="B82" s="1" t="str">
+        <v>SIN_CONTACTAR</v>
+      </c>
+      <c r="C82" s="1" t="str">
+        <v>Sin contactar</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="str">
+        <v>Resultado</v>
+      </c>
+      <c r="B83" s="1" t="str">
+        <v>WON</v>
+      </c>
+      <c r="C83" s="1" t="str">
+        <v>Ganado</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="str">
+        <v>Resultado</v>
+      </c>
+      <c r="B84" s="1" t="str">
+        <v>LOST</v>
+      </c>
+      <c r="C84" s="1" t="str">
+        <v>Perdido</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="str">
+        <v>Resultado</v>
+      </c>
+      <c r="B85" s="1" t="str">
+        <v>PARTIAL</v>
+      </c>
+      <c r="C85" s="1" t="str">
+        <v>Parcial</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B86" s="1" t="str">
+        <v>PRECIO</v>
+      </c>
+      <c r="C86" s="1" t="str">
+        <v>Precio</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B87" s="1" t="str">
+        <v>PLAZO_ENTREGA</v>
+      </c>
+      <c r="C87" s="1" t="str">
+        <v>Plazo de entrega</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B88" s="1" t="str">
+        <v>COMPETENCIA</v>
+      </c>
+      <c r="C88" s="1" t="str">
+        <v>Competencia</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B89" s="1" t="str">
+        <v>ESPECIFICACION_TECNICA</v>
+      </c>
+      <c r="C89" s="1" t="str">
+        <v>Especificación técnica</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B90" s="1" t="str">
+        <v>CREDITO</v>
+      </c>
+      <c r="C90" s="1" t="str">
+        <v>Crédito</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B91" s="1" t="str">
+        <v>PROYECTO_CANCELADO</v>
+      </c>
+      <c r="C91" s="1" t="str">
+        <v>Proyecto cancelado</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="str">
+        <v>Motivo del resultado</v>
+      </c>
+      <c r="B92" s="1" t="str">
+        <v>OTRO</v>
+      </c>
+      <c r="C92" s="1" t="str">
+        <v>Otro</v>
       </c>
     </row>
   </sheetData>
